--- a/data/trans_camb/IMC_inf_MED_R2-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IMC_inf_MED_R2-Dificultad-trans_camb.xlsx
@@ -601,22 +601,22 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>-6.77980861614686</v>
+        <v>-7.253196558237118</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>-0.2668926984446651</v>
+        <v>-0.3630500655649405</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>-12.30810501186865</v>
+        <v>-13.36657575158289</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-22.85818724749291</v>
+        <v>-19.15403974433966</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-9.293736830487608</v>
+        <v>-10.0271004708096</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>-9.394222033374222</v>
+        <v>-8.061981137315598</v>
       </c>
     </row>
     <row r="5">
@@ -627,22 +627,22 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>-14.27438183120049</v>
+        <v>-14.89960932541298</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>-15.50552301088783</v>
+        <v>-15.89728546727061</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>-20.97549198049061</v>
+        <v>-20.97234385382245</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>-36.33991228439393</v>
+        <v>-33.5980336981389</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-15.05482152113466</v>
+        <v>-15.63380592343893</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>-21.30446118694121</v>
+        <v>-18.58855672892151</v>
       </c>
     </row>
     <row r="6">
@@ -653,22 +653,22 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>2.802754238695479</v>
+        <v>0.08640996260021871</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>15.55129326376334</v>
+        <v>13.1168997990172</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>-3.726111984485172</v>
+        <v>-5.210750708100338</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>-7.794878400897823</v>
+        <v>-5.406539127563651</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-3.054802194604811</v>
+        <v>-4.588815437007053</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>1.569948250437621</v>
+        <v>3.194526126335723</v>
       </c>
     </row>
     <row r="7">
@@ -679,22 +679,22 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>-0.1235841590441265</v>
+        <v>-0.1344550531773973</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>-0.004864991264465382</v>
+        <v>-0.006729986631364062</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>-0.2529248785791577</v>
+        <v>-0.2750883430265414</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>-0.4697233431577659</v>
+        <v>-0.3941961766019951</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.1793088601596234</v>
+        <v>-0.1952767750717322</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.1812475730284235</v>
+        <v>-0.157006273325694</v>
       </c>
     </row>
     <row r="8">
@@ -705,22 +705,22 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>-0.2459229784171193</v>
+        <v>-0.2544748315875909</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>-0.2729499103846843</v>
+        <v>-0.28176297963727</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>-0.3958879129111306</v>
+        <v>-0.391837357255119</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>-0.7198620490073341</v>
+        <v>-0.6682894571163545</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.2699837629065979</v>
+        <v>-0.2907035241380348</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.3965121823427135</v>
+        <v>-0.3563548866930351</v>
       </c>
     </row>
     <row r="9">
@@ -731,22 +731,22 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>0.05523402431188067</v>
+        <v>0.001668301941512505</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.2952031105599089</v>
+        <v>0.2559787761891222</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>-0.08469057969901171</v>
+        <v>-0.1061417798377099</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>-0.1660157459369957</v>
+        <v>-0.1137555689549067</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-0.06093663827419485</v>
+        <v>-0.096127405293705</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.03646838199839619</v>
+        <v>0.06278450912704403</v>
       </c>
     </row>
     <row r="10">
@@ -761,22 +761,22 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>-15.89115090020206</v>
+        <v>-11.33876724091671</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>-19.78164860803431</v>
+        <v>-17.06972134796085</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-9.409979921637001</v>
+        <v>-8.518321456192979</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>-13.19412348964876</v>
+        <v>-12.97356177424872</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-12.77979533140486</v>
+        <v>-9.92129213510038</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>-16.09806570790782</v>
+        <v>-14.49961273219575</v>
       </c>
     </row>
     <row r="11">
@@ -787,22 +787,22 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>-25.547871655552</v>
+        <v>-19.69614898645889</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>-30.59684603635163</v>
+        <v>-27.91652412189153</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>-18.7600315544915</v>
+        <v>-16.00734443180836</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>-25.03834219189496</v>
+        <v>-23.78957308304265</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-19.05347187384449</v>
+        <v>-15.83207371212214</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>-24.39445966697444</v>
+        <v>-22.16186772161347</v>
       </c>
     </row>
     <row r="12">
@@ -813,22 +813,22 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>-7.000493166541245</v>
+        <v>-3.314203349468831</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>-5.89159345574295</v>
+        <v>-4.552520619978552</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>-0.5635930396484538</v>
+        <v>1.037078634219902</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>-0.4648826197471047</v>
+        <v>-0.7268757455040147</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-5.952612162774876</v>
+        <v>-3.678252138075555</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>-7.258337260747324</v>
+        <v>-6.150014863189755</v>
       </c>
     </row>
     <row r="13">
@@ -839,22 +839,22 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>-0.2740018241306523</v>
+        <v>-0.2063166645135096</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>-0.3410834015076946</v>
+        <v>-0.3105953140988548</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>-0.2124025475900881</v>
+        <v>-0.1972471163000992</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>-0.297818429556446</v>
+        <v>-0.3004110212642091</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.2489664217054528</v>
+        <v>-0.2019766132205855</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.3136104852812606</v>
+        <v>-0.2951815784456133</v>
       </c>
     </row>
     <row r="14">
@@ -865,22 +865,22 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>-0.4076318793265735</v>
+        <v>-0.3357131523731739</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>-0.5042521496061979</v>
+        <v>-0.4838942837846102</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>-0.3763221518123804</v>
+        <v>-0.34744168092257</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>-0.5295654529430147</v>
+        <v>-0.5101038086017967</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.3541397562265629</v>
+        <v>-0.3025321901694694</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.4629393329059761</v>
+        <v>-0.4277464881013577</v>
       </c>
     </row>
     <row r="15">
@@ -891,22 +891,22 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>-0.1322405408248852</v>
+        <v>-0.06642189498618564</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>-0.1075824519434355</v>
+        <v>-0.08487794254291041</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>-0.01388369620371375</v>
+        <v>0.02814985628863536</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>-0.01457328981477819</v>
+        <v>-0.01589653387546502</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.1212496159887878</v>
+        <v>-0.07643619418367478</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.1476393871200705</v>
+        <v>-0.1261196052267819</v>
       </c>
     </row>
     <row r="16">
@@ -921,22 +921,22 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>-4.413364083744925</v>
+        <v>-1.792323136840845</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>-4.95571472456085</v>
+        <v>-1.803629819182884</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>-3.276382519429216</v>
+        <v>-5.128158065843813</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>-10.39017993429944</v>
+        <v>-10.05857260355917</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-3.799011078948911</v>
+        <v>-3.48157303671397</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>-6.636125926040331</v>
+        <v>-4.930194908383645</v>
       </c>
     </row>
     <row r="17">
@@ -947,22 +947,22 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>-16.03766798417186</v>
+        <v>-12.47421595530296</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>-16.45061613720606</v>
+        <v>-12.20718733734422</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>-14.10908016467872</v>
+        <v>-14.73820947893546</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>-21.66796197383413</v>
+        <v>-19.93638981430395</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-11.57925865265191</v>
+        <v>-11.6660637244925</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>-14.50721168602243</v>
+        <v>-12.59892476154331</v>
       </c>
     </row>
     <row r="18">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>7.494517385132964</v>
+        <v>8.406271729533877</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>7.173807262160335</v>
+        <v>9.366751093454704</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>7.34335460286782</v>
+        <v>4.297933884921363</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.2554647556454958</v>
+        <v>0.9151960472957561</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>4.581997313726358</v>
+        <v>3.144406023416277</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>1.528295096419028</v>
+        <v>3.363338277268082</v>
       </c>
     </row>
     <row r="19">
@@ -999,22 +999,22 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>-0.09080659575148414</v>
+        <v>-0.03883424507711598</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>-0.101965660460766</v>
+        <v>-0.03907922683517873</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>-0.08578681662700437</v>
+        <v>-0.1315422682496058</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>-0.2720501820100688</v>
+        <v>-0.2580122216665338</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.08758102321050217</v>
+        <v>-0.08171203855229922</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.1529868396480582</v>
+        <v>-0.1157109939030386</v>
       </c>
     </row>
     <row r="20">
@@ -1025,22 +1025,22 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>-0.2939636407444265</v>
+        <v>-0.243620439494899</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>-0.3100344239662753</v>
+        <v>-0.2477408363609737</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>-0.3295920250499925</v>
+        <v>-0.3339665258693915</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>-0.5128531503491309</v>
+        <v>-0.4796250599636919</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.2464394378351567</v>
+        <v>-0.2413608593193246</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.3161104538223449</v>
+        <v>-0.2763510292845481</v>
       </c>
     </row>
     <row r="21">
@@ -1051,22 +1051,22 @@
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>0.1823981267654796</v>
+        <v>0.2161530191250727</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>0.1656836412529638</v>
+        <v>0.2277914539574854</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>0.2334889479330904</v>
+        <v>0.1308875981483208</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>0.003554327981858404</v>
+        <v>0.02557405417178311</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.1177138146085791</v>
+        <v>0.07815598824866134</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.03590865904445613</v>
+        <v>0.08319616332997108</v>
       </c>
     </row>
     <row r="22">
@@ -1081,22 +1081,22 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>0.2898482570057093</v>
+        <v>-4.637863577879997</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>-15.73392458804063</v>
+        <v>-18.22731761567192</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>-17.92520869446988</v>
+        <v>-18.31611378177978</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>-22.62346210617608</v>
+        <v>-22.94334011105084</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-7.968446189337191</v>
+        <v>-10.53263775957115</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>-18.99252999962823</v>
+        <v>-20.43548819225481</v>
       </c>
     </row>
     <row r="23">
@@ -1107,22 +1107,22 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>-13.06804702212963</v>
+        <v>-18.14496681430116</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>-29.5772944379085</v>
+        <v>-31.60017302774649</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>-32.88261813815335</v>
+        <v>-31.9545946773709</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>-36.49124541439809</v>
+        <v>-36.10666830747029</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-18.40735209981338</v>
+        <v>-19.55835031312782</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>-28.56977303742277</v>
+        <v>-29.8926584243533</v>
       </c>
     </row>
     <row r="24">
@@ -1133,22 +1133,22 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>15.42426145294361</v>
+        <v>8.257834635201538</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>-0.2778829536382262</v>
+        <v>-4.074614373531555</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>-3.412199208499559</v>
+        <v>-3.485367923767142</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>-8.8450010278503</v>
+        <v>-7.573233358706418</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>3.492173674615549</v>
+        <v>-0.2796519881900565</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>-9.008676211771812</v>
+        <v>-10.49156746852922</v>
       </c>
     </row>
     <row r="25">
@@ -1159,22 +1159,22 @@
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>0.006356939150627169</v>
+        <v>-0.09708647181004716</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>-0.3450757380430298</v>
+        <v>-0.3815605888682947</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>-0.3705803410211383</v>
+        <v>-0.3705486754897542</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>-0.4677106105309684</v>
+        <v>-0.4641609235862006</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.1698164245439726</v>
+        <v>-0.2169671352052957</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.4047518752020682</v>
+        <v>-0.4209609625628768</v>
       </c>
     </row>
     <row r="26">
@@ -1185,22 +1185,22 @@
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>-0.2556870153422688</v>
+        <v>-0.3316307868735567</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>-0.5817602945237043</v>
+        <v>-0.5817062053615294</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>-0.6024046595371451</v>
+        <v>-0.5827361304444647</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>-0.6665662163628967</v>
+        <v>-0.6419154130608327</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-0.3574656669015214</v>
+        <v>-0.3805776196373495</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.5560608215930906</v>
+        <v>-0.5762335604225686</v>
       </c>
     </row>
     <row r="27">
@@ -1211,22 +1211,22 @@
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>0.3964460325927416</v>
+        <v>0.210631017512938</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>-0.0148258260262598</v>
+        <v>-0.09893007370477896</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>-0.0769351103455871</v>
+        <v>-0.07192094623256801</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>-0.2003825819443312</v>
+        <v>-0.1701855675270972</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.07194248070397724</v>
+        <v>-0.006799961101978459</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.2123399934765408</v>
+        <v>-0.2326919578991924</v>
       </c>
     </row>
     <row r="28">
@@ -1241,22 +1241,22 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>-8.078265558976433</v>
+        <v>-6.818968803456171</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>-12.52945790540877</v>
+        <v>-10.9057954374884</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>-9.971070860787034</v>
+        <v>-10.50294136284147</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>-16.8979910722836</v>
+        <v>-15.97324983361676</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-8.916851181907203</v>
+        <v>-8.494614051367016</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>-13.97991586020547</v>
+        <v>-12.76642608997153</v>
       </c>
     </row>
     <row r="29">
@@ -1267,22 +1267,22 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>-12.99831110404673</v>
+        <v>-11.94667589482128</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>-18.87142744832819</v>
+        <v>-16.98855529420571</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>-14.6824349456093</v>
+        <v>-14.94744179681027</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>-23.54192309821056</v>
+        <v>-21.96367645137428</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-12.43857831799006</v>
+        <v>-11.67764209679449</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>-18.49346273042028</v>
+        <v>-17.00401017509923</v>
       </c>
     </row>
     <row r="30">
@@ -1293,22 +1293,22 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>-2.65907914779198</v>
+        <v>-2.148572797597953</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>-5.687912677866044</v>
+        <v>-4.759345070731889</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>-4.716424686909929</v>
+        <v>-5.475366457666341</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>-10.93089142801198</v>
+        <v>-10.27524944969567</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-5.185393223430313</v>
+        <v>-4.940816299027168</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>-9.368010035277097</v>
+        <v>-8.180789068035994</v>
       </c>
     </row>
     <row r="31">
@@ -1319,22 +1319,22 @@
         </is>
       </c>
       <c r="C31" s="6" t="n">
-        <v>-0.1513851192904668</v>
+        <v>-0.1318125273960864</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>-0.2347995947654292</v>
+        <v>-0.2108120012444479</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>-0.2218898567799895</v>
+        <v>-0.2343465167524963</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>-0.3760371249234703</v>
+        <v>-0.3564025857526801</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-0.1811025116224433</v>
+        <v>-0.1756665397152637</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-0.2839340730156854</v>
+        <v>-0.2640065672430475</v>
       </c>
     </row>
     <row r="32">
@@ -1345,22 +1345,22 @@
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>-0.2370561553891401</v>
+        <v>-0.2191944454999714</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>-0.3458454257657425</v>
+        <v>-0.3196548917653996</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>-0.3083092933771612</v>
+        <v>-0.318958759090554</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>-0.5041525813036314</v>
+        <v>-0.4728827812154072</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-0.2430522759243333</v>
+        <v>-0.2325186288690091</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.3603829443703235</v>
+        <v>-0.3449081001768823</v>
       </c>
     </row>
     <row r="33">
@@ -1371,22 +1371,22 @@
         </is>
       </c>
       <c r="C33" s="6" t="n">
-        <v>-0.05082493616357237</v>
+        <v>-0.04330625294739594</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>-0.1108354392099048</v>
+        <v>-0.09488458987803339</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>-0.1105047700938643</v>
+        <v>-0.1330854183854229</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>-0.2483188133832003</v>
+        <v>-0.2383043214846716</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-0.107896812259758</v>
+        <v>-0.104533201768002</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-0.1949784792262749</v>
+        <v>-0.174424551358311</v>
       </c>
     </row>
     <row r="34">
